--- a/file_upload_forms/032_training_assignment_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/032_training_assignment_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Submit Training Assignment</t>
+          <t>What type of file is this?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>uploaded_files</t>
+          <t>description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Files</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,63 +561,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>training_assignment_submission_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Submit Training Assignment</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_4</t>
+          <t>submitted_by</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Submit Training Assignment</t>
+          <t>Who submitted this?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>submitted_by</t>
+          <t>date_submitted</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Submitted By</t>
+          <t>Date Submitted</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>date_submitted</t>
+          <t>time_submitted</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Date Submitted</t>
+          <t>Time Submitted</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,30 +653,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>time_submitted</t>
+          <t>training_assignment_submission_form_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Time Submitted</t>
+          <t>Training Assignment Submission Form 7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,20 +686,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Submit Training Assignment</t>
+          <t>Training Assignment Submission Form 8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submit Training Assignment</t>
+          <t>Training Assignment Submission Form 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submit Training Assignment</t>
+          <t>Training Assignment Submission Form</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -803,63 +803,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_4_choices</t>
+          <t>training_assignment_submission_form_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_4_choices</t>
+          <t>training_assignment_submission_form_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_4_choices</t>
+          <t>training_assignment_submission_form_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -888,97 +888,97 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_8_choices</t>
+          <t>training_assignment_submission_form_7_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_8_choices</t>
+          <t>training_assignment_submission_form_7_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_8_choices</t>
+          <t>training_assignment_submission_form_7_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_9_choices</t>
+          <t>training_assignment_submission_form_8_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>training_assignment_submission_form_9_choices</t>
+          <t>training_assignment_submission_form_8_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
